--- a/OCT_2026/10-27-26/LMT/Jalal Sons ok.xlsx
+++ b/OCT_2026/10-27-26/LMT/Jalal Sons ok.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998D218A-1C53-4F46-97A6-84C9009C2B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A899E0-C63E-49DD-A987-55BC3C49D8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,13 +49,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'1'!$A$1:$P$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3976" uniqueCount="520">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1614,7 +1615,7 @@
     <t>Invoice No # :185616</t>
   </si>
   <si>
-    <t>ok</t>
+    <t>NTN #: 8252485-7 STRN #: 3277876394130</t>
   </si>
 </sst>
 </file>
@@ -47899,7 +47900,7 @@
       <c r="L4" s="396"/>
       <c r="M4" s="399">
         <f ca="1">TODAY()+1</f>
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="N4" s="399"/>
       <c r="O4" s="399"/>
@@ -47927,7 +47928,7 @@
       <c r="L5" s="396"/>
       <c r="M5" s="399">
         <f ca="1">M4-1</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="N5" s="395"/>
       <c r="O5" s="395"/>
@@ -54120,7 +54121,7 @@
       <c r="G3" s="391"/>
       <c r="H3" s="388">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="I3" s="388"/>
       <c r="J3" s="389"/>
@@ -55566,7 +55567,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:XFD38"/>
+  <dimension ref="A2:XFD38"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -55590,11 +55591,6 @@
     <col min="22" max="22" width="5.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
-      <c r="J1" t="s">
-        <v>519</v>
-      </c>
-    </row>
     <row r="2" spans="1:22 16383:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="394" t="s">
         <v>91</v>
@@ -55705,7 +55701,7 @@
     </row>
     <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="396" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B7" s="396"/>
       <c r="C7" s="396"/>
@@ -56981,7 +56977,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
